--- a/artfynd/A 13969-2024 artfynd.xlsx
+++ b/artfynd/A 13969-2024 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>121769914</v>
       </c>
       <c r="B22" t="n">
-        <v>91187</v>
+        <v>91201</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 13969-2024 artfynd.xlsx
+++ b/artfynd/A 13969-2024 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>121769914</v>
       </c>
       <c r="B22" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 13969-2024 artfynd.xlsx
+++ b/artfynd/A 13969-2024 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>121769914</v>
       </c>
       <c r="B22" t="n">
-        <v>91203</v>
+        <v>91204</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 13969-2024 artfynd.xlsx
+++ b/artfynd/A 13969-2024 artfynd.xlsx
@@ -3022,7 +3022,7 @@
         <v>121769914</v>
       </c>
       <c r="B22" t="n">
-        <v>91204</v>
+        <v>91213</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 13969-2024 artfynd.xlsx
+++ b/artfynd/A 13969-2024 artfynd.xlsx
@@ -1705,11 +1705,11 @@
         <v>116781214</v>
       </c>
       <c r="B11" t="n">
-        <v>57284</v>
+        <v>57390</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -2059,11 +2059,11 @@
         <v>116773651</v>
       </c>
       <c r="B14" t="n">
-        <v>57284</v>
+        <v>57390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">

--- a/artfynd/A 13969-2024 artfynd.xlsx
+++ b/artfynd/A 13969-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116772287</v>
+        <v>116770695</v>
       </c>
       <c r="B2" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325095</v>
+        <v>325188</v>
       </c>
       <c r="R2" t="n">
-        <v>6569150</v>
+        <v>6569164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal murken granlåga ca 40m från vägen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,54 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116780569</v>
+        <v>116779031</v>
       </c>
       <c r="B3" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Storstensåsen, Storstensåsen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325116</v>
+        <v>325035</v>
       </c>
       <c r="R3" t="n">
-        <v>6569009</v>
+        <v>6569284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,53 +894,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116780286</v>
+        <v>116779510</v>
       </c>
       <c r="B4" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Storstensåsen, Storstensåsen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325154</v>
+        <v>325018</v>
       </c>
       <c r="R4" t="n">
-        <v>6569082</v>
+        <v>6569239</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,14 +962,19 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hörde den</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,57 +1001,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116772505</v>
+        <v>121769914</v>
       </c>
       <c r="B5" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Storstensåsen S., Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325094</v>
+        <v>325175</v>
       </c>
       <c r="R5" t="n">
-        <v>6569121</v>
+        <v>6569087</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,22 +1069,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,72 +1083,93 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116778626</v>
+        <v>116773651</v>
       </c>
       <c r="B6" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storstensåsen (Storstensåsen), Dls</t>
+          <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325084</v>
+        <v>325150</v>
       </c>
       <c r="R6" t="n">
-        <v>6569312</v>
+        <v>6569079</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,50 +1238,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116770729</v>
+        <v>116781214</v>
       </c>
       <c r="B7" t="n">
-        <v>96733</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325188</v>
+        <v>325215</v>
       </c>
       <c r="R7" t="n">
-        <v>6569161</v>
+        <v>6569080</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,54 +1354,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116771835</v>
+        <v>116771912</v>
       </c>
       <c r="B8" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Storstensåsen, Storstensåsen, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325100</v>
+        <v>325089</v>
       </c>
       <c r="R8" t="n">
-        <v>6569179</v>
+        <v>6569197</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1439,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Massor med hackmärken i stående död tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,54 +1471,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116773817</v>
+        <v>116778555</v>
       </c>
       <c r="B9" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Storstensåsen, Storstensåsen, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325084</v>
+        <v>325090</v>
       </c>
       <c r="R9" t="n">
-        <v>6569117</v>
+        <v>6569324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1551,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackmärken i död tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,15 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116779510</v>
+        <v>116780249</v>
       </c>
       <c r="B10" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,34 +1594,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storstensåsen (Storstensåsen), Dls</t>
+          <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325018</v>
+        <v>325055</v>
       </c>
       <c r="R10" t="n">
-        <v>6569239</v>
+        <v>6569004</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1663,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hack i granhögstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,32 +1695,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116781214</v>
+        <v>116780286</v>
       </c>
       <c r="B11" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1735,29 +1723,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325215</v>
+        <v>325154</v>
       </c>
       <c r="R11" t="n">
-        <v>6569080</v>
+        <v>6569082</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1784,19 +1763,14 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:34</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hörde den</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,50 +1797,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116780249</v>
+        <v>116771835</v>
       </c>
       <c r="B12" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325055</v>
+        <v>325100</v>
       </c>
       <c r="R12" t="n">
-        <v>6569004</v>
+        <v>6569179</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,7 +1871,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,12 +1881,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska hack i granhögstubbe</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,15 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116780805</v>
+        <v>116771997</v>
       </c>
       <c r="B13" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,19 +1938,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>87</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Storstensåsen, Storstensåsen, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325120</v>
+        <v>325094</v>
       </c>
       <c r="R13" t="n">
-        <v>6569006</v>
+        <v>6569197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,47 +2019,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116773651</v>
+        <v>116772287</v>
       </c>
       <c r="B14" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2105,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325150</v>
+        <v>325095</v>
       </c>
       <c r="R14" t="n">
-        <v>6569079</v>
+        <v>6569150</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2150,7 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,50 +2130,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116779031</v>
+        <v>116772505</v>
       </c>
       <c r="B15" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storstensåsen (Storstensåsen), Dls</t>
+          <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325035</v>
+        <v>325094</v>
       </c>
       <c r="R15" t="n">
-        <v>6569284</v>
+        <v>6569121</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2204,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2214,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,50 +2241,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116778555</v>
+        <v>116773817</v>
       </c>
       <c r="B16" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storstensåsen (Storstensåsen), Dls</t>
+          <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>325090</v>
+        <v>325084</v>
       </c>
       <c r="R16" t="n">
-        <v>6569324</v>
+        <v>6569117</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,7 +2315,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,12 +2325,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hackmärken i död tall</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,50 +2352,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116771020</v>
+        <v>116778316</v>
       </c>
       <c r="B17" t="n">
-        <v>96730</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>325169</v>
+        <v>325161</v>
       </c>
       <c r="R17" t="n">
-        <v>6569194</v>
+        <v>6569262</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,7 +2426,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2491,7 +2436,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,50 +2463,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116770695</v>
+        <v>116778626</v>
       </c>
       <c r="B18" t="n">
-        <v>94399</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bråtet (Bråtet), Dls</t>
+          <t>Storstensåsen, Storstensåsen, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>325188</v>
+        <v>325084</v>
       </c>
       <c r="R18" t="n">
-        <v>6569164</v>
+        <v>6569312</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,7 +2537,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2603,12 +2547,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gammal murken granlåga ca 40m från vägen</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2635,15 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119485068</v>
+        <v>116780569</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2673,28 +2607,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bråtet 2, Dls</t>
+          <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
         <v>325116</v>
       </c>
       <c r="R19" t="n">
-        <v>6569008</v>
+        <v>6569009</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2719,35 +2641,39 @@
           <t>Torrskog</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>OD-Ben-0414</t>
-        </is>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Claes Kannesten</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -2755,23 +2681,14 @@
           <t>Roger Adolfsson</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119485081</v>
+        <v>116780805</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2798,31 +2715,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>37</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bråtet 3, Dls</t>
+          <t>Bråtet, Bråtet, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>325085</v>
+        <v>325120</v>
       </c>
       <c r="R20" t="n">
-        <v>6569117</v>
+        <v>6569006</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2847,35 +2752,39 @@
           <t>Torrskog</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>OD-Ben-0415</t>
-        </is>
-      </c>
       <c r="Y20" t="inlineStr">
         <is>
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Claes Kannesten</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2883,23 +2792,14 @@
           <t>Roger Adolfsson</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119485216</v>
+        <v>119485081</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2826,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2943,14 +2843,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storstensåsen 2, Dls</t>
+          <t>Bråtet 3, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>325084</v>
+        <v>325085</v>
       </c>
       <c r="R21" t="n">
-        <v>6569311</v>
+        <v>6569117</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2977,7 +2877,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>OD-Ben-0421</t>
+          <t>OD-Ben-0033</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3019,56 +2919,64 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121769914</v>
+        <v>119485200</v>
       </c>
       <c r="B22" t="n">
-        <v>91222</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5467</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storstensåsen S., Dls</t>
+          <t>Storstensåsen 1, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>325175</v>
+        <v>325095</v>
       </c>
       <c r="R22" t="n">
-        <v>6569087</v>
+        <v>6569197</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3090,14 +2998,19 @@
           <t>Torrskog</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>OD-Ben-0030</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,38 +3023,359 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Claes Kannesten</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>119485216</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storstensåsen 2, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>325084</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6569311</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>OD-Ben-0022</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Claes Kannesten</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>116771020</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bråtet, Bråtet, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>325169</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6569194</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>116770729</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bråtet, Bråtet, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>325188</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6569161</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Torrskog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13969-2024 artfynd.xlsx
+++ b/artfynd/A 13969-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116770695</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116779031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116779510</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121769914</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116773651</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1351,6 +1381,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116781214</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116771912</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1580,6 +1620,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116778555</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1692,6 +1737,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116780249</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116780286</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1905,6 +1960,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116771835</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116771997</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2127,6 +2192,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116772287</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2238,6 +2308,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116772505</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2349,6 +2424,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116773817</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2460,6 +2540,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116778316</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2571,6 +2656,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116778626</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2682,6 +2772,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116780569</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2793,6 +2888,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116780805</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2916,6 +3016,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119485081</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3039,6 +3144,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119485200</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3162,6 +3272,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119485216</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3269,6 +3384,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116771020</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3376,8 +3496,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116770729</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>